--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3563,6 +3563,122 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129854207</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58453</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Björnmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>574841</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6521200</v>
+      </c>
+      <c r="S25" t="n">
+        <v>125</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Karlsson, Jan Gustafsson, Lars Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Karlsson, Jan Gustafsson, Lars Danielsson</t>
+          <t>Lars Danielsson, Jan Gustafsson, Jan Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>129854207</v>
       </c>
       <c r="B25" t="n">
-        <v>58453</v>
+        <v>58456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Danielsson, Jan Gustafsson, Jan Karlsson</t>
+          <t>Jan Karlsson, Jan Gustafsson, Lars Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>129854207</v>
       </c>
       <c r="B25" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>129854207</v>
       </c>
       <c r="B25" t="n">
-        <v>58459</v>
+        <v>58460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Danielsson, Jan Gustafsson, Jan Karlsson</t>
+          <t>Jan Karlsson, Jan Gustafsson, Lars Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>129854207</v>
       </c>
       <c r="B25" t="n">
-        <v>58461</v>
+        <v>58546</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>129854207</v>
       </c>
       <c r="B25" t="n">
-        <v>58546</v>
+        <v>58461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,6 +3679,366 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130581035</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SV om Djupviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>574941</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6521204</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Fågelinventering Ålsjön 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130581098</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SV om Djupviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>574844</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6521260</v>
+      </c>
+      <c r="S27" t="n">
+        <v>100</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Fågelinventering Ålsjön 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130581028</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SV om Djupviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>574826</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6521265</v>
+      </c>
+      <c r="S28" t="n">
+        <v>100</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Fågelinventering Ålsjön 2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>130581035</v>
       </c>
       <c r="B26" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>130581098</v>
       </c>
       <c r="B27" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130581028</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>130581035</v>
       </c>
       <c r="B26" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>130581098</v>
       </c>
       <c r="B27" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130581028</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>130581035</v>
       </c>
       <c r="B26" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>130581098</v>
       </c>
       <c r="B27" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130581028</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>130581035</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>130581098</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130581028</v>
       </c>
       <c r="B28" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -3684,7 +3684,7 @@
         <v>130581035</v>
       </c>
       <c r="B26" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>130581098</v>
       </c>
       <c r="B27" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130581028</v>
       </c>
       <c r="B28" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2025 artfynd.xlsx
+++ b/artfynd/A 27954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1673539</v>
+        <v>278111</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574652.5882885446</v>
+        <v>575189</v>
       </c>
       <c r="R2" t="n">
-        <v>6521255.326444337</v>
+        <v>6521052</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sammanvuxna, trolige fler ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Talldominerad barrblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,45 +787,36 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3426241</v>
+        <v>320443</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574641.2687815793</v>
+        <v>574989</v>
       </c>
       <c r="R3" t="n">
-        <v>6521223.514627249</v>
+        <v>6521294</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,23 +889,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1403318</v>
+        <v>1159170</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,43 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574683.3521586772</v>
+        <v>574898</v>
       </c>
       <c r="R4" t="n">
-        <v>6521193.769663655</v>
+        <v>6521343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,22 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +977,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,67 +991,49 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1673537</v>
+        <v>1159171</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574683.3521586772</v>
+        <v>575178</v>
       </c>
       <c r="R5" t="n">
-        <v>6521193.769663655</v>
+        <v>6521067</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,22 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1079,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,50 +1093,41 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1403319</v>
+        <v>1152170</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1235,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574653.0457777885</v>
+        <v>575199</v>
       </c>
       <c r="R6" t="n">
-        <v>6521285.374535304</v>
+        <v>6521023</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,22 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Talldominerad barrblandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1308,23 +1204,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1319792</v>
+        <v>1211978</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,43 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574706.1467286987</v>
+        <v>575064</v>
       </c>
       <c r="R7" t="n">
-        <v>6521141.898902641</v>
+        <v>6521235</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1395,22 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1292,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1438,67 +1306,49 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1673538</v>
+        <v>1211979</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574641.2687815793</v>
+        <v>575052</v>
       </c>
       <c r="R8" t="n">
-        <v>6521223.514627249</v>
+        <v>6521227</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1525,22 +1375,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,7 +1394,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1568,23 +1408,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1673536</v>
+        <v>1315843</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,26 +1423,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1625,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574706.1467286987</v>
+        <v>574890</v>
       </c>
       <c r="R9" t="n">
-        <v>6521141.898902641</v>
+        <v>6521260</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1655,22 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1684,7 +1505,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1698,23 +1519,14 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1673540</v>
+        <v>1315844</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,26 +1534,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1755,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574653.0457777885</v>
+        <v>574970</v>
       </c>
       <c r="R10" t="n">
-        <v>6521285.374535304</v>
+        <v>6521204</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1785,22 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,7 +1616,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Talldominerad drygt 100-årig barrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1828,50 +1630,41 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kyrkkärret</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1400523</v>
+        <v>1319792</v>
       </c>
       <c r="B11" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1885,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575100.1774213741</v>
+        <v>574706</v>
       </c>
       <c r="R11" t="n">
-        <v>6521051.123379614</v>
+        <v>6521142</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1915,22 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,7 +1727,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog</t>
+          <t>Talldominerad drygt 100-årig barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1958,50 +1741,62 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5985566</v>
+        <v>1400523</v>
       </c>
       <c r="B12" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575172.4310845876</v>
+        <v>575100</v>
       </c>
       <c r="R12" t="n">
-        <v>6521017.824663047</v>
+        <v>6521051</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2031,19 +1826,9 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2075,15 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1760337</v>
+        <v>1403317</v>
       </c>
       <c r="B13" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2091,26 +1871,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2124,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574800.9545052134</v>
+        <v>574663</v>
       </c>
       <c r="R13" t="n">
-        <v>6521149.429286305</v>
+        <v>6521136</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2154,22 +1934,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>troligen med tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,7 +1958,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog, hällmark</t>
+          <t>Talldominerad drygt 100-årig barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2197,46 +1972,45 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1315843</v>
+        <v>1403318</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2250,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574889.6067937308</v>
+        <v>574683</v>
       </c>
       <c r="R14" t="n">
-        <v>6521260.428338087</v>
+        <v>6521194</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2280,22 +2054,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2309,7 +2073,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Talldominerad drygt 100-årig barrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2323,41 +2087,40 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1315844</v>
+        <v>1403319</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2376,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574970.0764099346</v>
+        <v>574653</v>
       </c>
       <c r="R15" t="n">
-        <v>6521204.498250298</v>
+        <v>6521285</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2406,22 +2169,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2435,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Talldominerad drygt 100-årig barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2449,19 +2202,18 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1669599</v>
+        <v>1444147</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,26 +2221,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2502,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575051.845242527</v>
+        <v>575330</v>
       </c>
       <c r="R16" t="n">
-        <v>6521215.407429985</v>
+        <v>6520969</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2535,21 +2287,11 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2561,7 +2303,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Talldominerad barrblandskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2579,42 +2321,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1760327</v>
+        <v>1476431</v>
       </c>
       <c r="B17" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2628,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575051.845242527</v>
+        <v>575080</v>
       </c>
       <c r="R17" t="n">
-        <v>6521215.407429985</v>
+        <v>6521207</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2661,19 +2398,9 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,46 +2432,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6223407</v>
+        <v>1624912</v>
       </c>
       <c r="B18" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224363</v>
+        <v>5448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575319.9535879208</v>
+        <v>575052</v>
       </c>
       <c r="R18" t="n">
-        <v>6520956.4686284</v>
+        <v>6521227</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2774,19 +2509,14 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sammanvuxna</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,7 +2530,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2818,15 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1760329</v>
+        <v>1760324</v>
       </c>
       <c r="B19" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,7 +2578,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2867,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575081.3874654402</v>
+        <v>575019</v>
       </c>
       <c r="R19" t="n">
-        <v>6521163.669939941</v>
+        <v>6521255</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2900,19 +2625,9 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2944,15 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1152170</v>
+        <v>1760327</v>
       </c>
       <c r="B20" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2960,26 +2670,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2993,10 +2703,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575199.3125698423</v>
+        <v>575052</v>
       </c>
       <c r="R20" t="n">
-        <v>6521023.008988188</v>
+        <v>6521215</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3026,21 +2736,11 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3052,7 +2752,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3070,15 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1760324</v>
+        <v>1760328</v>
       </c>
       <c r="B21" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3105,7 +2800,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3119,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575019.4329395456</v>
+        <v>575002</v>
       </c>
       <c r="R21" t="n">
-        <v>6521254.658605151</v>
+        <v>6521250</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3152,19 +2847,9 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3196,15 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1444147</v>
+        <v>1760329</v>
       </c>
       <c r="B22" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3212,26 +2892,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3245,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575330.095633588</v>
+        <v>575081</v>
       </c>
       <c r="R22" t="n">
-        <v>6520968.579367588</v>
+        <v>6521164</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3278,21 +2958,11 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3304,7 +2974,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3322,15 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1760328</v>
+        <v>1760337</v>
       </c>
       <c r="B23" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,7 +3022,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3371,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575001.888803825</v>
+        <v>574801</v>
       </c>
       <c r="R23" t="n">
-        <v>6521249.656907043</v>
+        <v>6521149</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3404,21 +3069,11 @@
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2011-09-13</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3430,7 +3085,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Talldominerad barrblandskog, hällmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3448,50 +3103,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3425958</v>
+        <v>1761350</v>
       </c>
       <c r="B24" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kyrkkärret-Björnmossenområdet, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575319.9535879208</v>
+        <v>574685</v>
       </c>
       <c r="R24" t="n">
-        <v>6520956.4686284</v>
+        <v>6521132</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3518,22 +3177,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3547,7 +3196,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Talldominerad barrblandskog</t>
+          <t>Talldominerad drygt 100-årig barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3561,61 +3210,65 @@
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129854207</v>
+        <v>130581028</v>
       </c>
       <c r="B25" t="n">
-        <v>58461</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnmossen, Srm</t>
+          <t>SV om Djupviken, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574841</v>
+        <v>574826</v>
       </c>
       <c r="R25" t="n">
-        <v>6521200</v>
+        <v>6521265</v>
       </c>
       <c r="S25" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,22 +3292,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3669,22 +3322,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Karlsson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Karlsson, Jan Gustafsson, Lars Danielsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Fågelinventering Ålsjön 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130581035</v>
+        <v>130581043</v>
       </c>
       <c r="B26" t="n">
-        <v>58043</v>
+        <v>58497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3692,21 +3349,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3725,13 +3382,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574941</v>
+        <v>574944</v>
       </c>
       <c r="R26" t="n">
-        <v>6521204</v>
+        <v>6521395</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3760,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3770,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,10 +3458,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130581098</v>
+        <v>130581035</v>
       </c>
       <c r="B27" t="n">
-        <v>58043</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3845,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574844</v>
+        <v>574941</v>
       </c>
       <c r="R27" t="n">
-        <v>6521260</v>
+        <v>6521204</v>
       </c>
       <c r="S27" t="n">
         <v>100</v>
@@ -3875,22 +3532,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3921,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130581028</v>
+        <v>130581098</v>
       </c>
       <c r="B28" t="n">
-        <v>57881</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3932,21 +3589,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3956,7 +3613,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3965,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574826</v>
+        <v>574844</v>
       </c>
       <c r="R28" t="n">
-        <v>6521265</v>
+        <v>6521260</v>
       </c>
       <c r="S28" t="n">
         <v>100</v>
@@ -3995,22 +3652,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4038,6 +3695,516 @@
           <t>Fågelinventering Ålsjön 2025</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3425958</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kyrkkärret-Björnmossenområdet, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575320</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6520956</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Talldominerad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3426241</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kyrkkärret-Björnmossenområdet, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>574641</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6521224</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2011-09-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2011-09-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Talldominerad drygt 100-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3426242</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kyrkkärret-Björnmossenområdet, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>574658</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6521414</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2011-09-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2011-09-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Talldominerad drygt 100-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kyrkkärret</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5985566</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kyrkkärret-Björnmossenområdet, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575172</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6521018</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Talldominerad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6223407</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kyrkkärret-Björnmossenområdet, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575320</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6520956</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Talldominerad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
